--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2689" uniqueCount="613">
   <si>
     <t>ID</t>
   </si>
@@ -1471,10 +1471,10 @@
     <t>/api/debug/db</t>
   </si>
   <si>
-    <t>⚠️ NO</t>
-  </si>
-  <si>
-    <t>⚠️ Public</t>
+    <t>✅ YES (Admin only)</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
   <si>
     <t>debugController.js</t>
@@ -1720,7 +1720,7 @@
     <t>Overall Security Score</t>
   </si>
   <si>
-    <t>58 / 100</t>
+    <t>58 / 100 — Pre-Remediation Baseline</t>
   </si>
   <si>
     <t>Needs Remediation</t>
@@ -1729,16 +1729,16 @@
     <t>Critical Findings</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>1 unique root cause (5 occurrences)</t>
+  </si>
+  <si>
+    <t>🚨 ACTION REQUIRED — Production Blocker</t>
   </si>
   <si>
     <t>High Findings</t>
   </si>
   <si>
-    <t>5</t>
+    <t>4 unique root causes (multi-occurrence)</t>
   </si>
   <si>
     <t>Action Required</t>
@@ -1747,13 +1747,13 @@
     <t>Medium Findings</t>
   </si>
   <si>
-    <t>4</t>
+    <t>4 unique root causes</t>
   </si>
   <si>
     <t>Low Findings</t>
   </si>
   <si>
-    <t>3</t>
+    <t>3 unique root causes</t>
   </si>
   <si>
     <t>Informational</t>
@@ -1777,58 +1777,82 @@
     <t>Authentication Bypass Risk</t>
   </si>
   <si>
-    <t>ACTIVE in codebase</t>
-  </si>
-  <si>
-    <t>🚨 Immediate Fix Required</t>
+    <t>FIXED — authController.js bypass removed</t>
+  </si>
+  <si>
+    <t>✅ Remediated</t>
+  </si>
+  <si>
+    <t>Mock Token System</t>
+  </si>
+  <si>
+    <t>FIXED — mock_token_ acceptance removed from auth middleware</t>
   </si>
   <si>
     <t>Unauthenticated Debug Routes</t>
   </si>
   <si>
-    <t>3 routes exposed</t>
+    <t>FIXED — authenticate + requireRole(admin) added to all /api/debug/* routes</t>
+  </si>
+  <si>
+    <t>Duplicate Route Registration</t>
+  </si>
+  <si>
+    <t>FIXED — duplicate GET /messages/:userId removed</t>
   </si>
   <si>
     <t>CORS Misconfiguration</t>
   </si>
   <si>
-    <t>Wildcard reflection active</t>
-  </si>
-  <si>
-    <t>High Priority Fix</t>
+    <t>FIXED — explicit allowlist applied, wildcard removed</t>
+  </si>
+  <si>
+    <t>Resume File Public Access</t>
+  </si>
+  <si>
+    <t>FIXED — /uploads/resumes/* now requires auth + ownership check</t>
+  </si>
+  <si>
+    <t>File Upload Validation</t>
+  </si>
+  <si>
+    <t>FIXED — magic-byte + MIME validation added</t>
+  </si>
+  <si>
+    <t>CSRF Disabled in Non-Prod</t>
+  </si>
+  <si>
+    <t>FIXED — CSRF now enabled in all environments</t>
+  </si>
+  <si>
+    <t>Rate Limiting Too Permissive</t>
+  </si>
+  <si>
+    <t>FIXED — tiered limits: auth=20/15min, API=200/15min, AI=50/hr</t>
   </si>
   <si>
     <t>IDOR Vulnerable Routes</t>
   </si>
   <si>
-    <t>8 routes identified</t>
-  </si>
-  <si>
-    <t>File Upload Validation</t>
-  </si>
-  <si>
-    <t>Extension-only (weak)</t>
+    <t>8 routes still require per-controller ownership checks</t>
+  </si>
+  <si>
+    <t>⚠️ Partial — Needs Controller Fixes</t>
+  </si>
+  <si>
+    <t>Dependency Vulnerabilities</t>
+  </si>
+  <si>
+    <t>1 (axios CVE-2023-45857 — update to &gt;=1.7.4)</t>
   </si>
   <si>
     <t>Medium Priority Fix</t>
   </si>
   <si>
-    <t>Rate Limiting</t>
-  </si>
-  <si>
-    <t>2000/15min (too permissive)</t>
-  </si>
-  <si>
-    <t>Dependency Vulnerabilities</t>
-  </si>
-  <si>
-    <t>1 (axios CVE-2023-45857)</t>
-  </si>
-  <si>
-    <t>Mock Token System</t>
-  </si>
-  <si>
-    <t>Active in production code</t>
+    <t>Stack Traces Exposed</t>
+  </si>
+  <si>
+    <t>FIXED — prod responses omit stack trace; logs written outside web root</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1949,15 +1973,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10740,10 +10761,10 @@
       <c r="C75" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>486</v>
       </c>
       <c r="F75" s="9" t="s">
@@ -10760,10 +10781,10 @@
       <c r="C76" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="9" t="s">
         <v>486</v>
       </c>
       <c r="F76" s="9" t="s">
@@ -10780,10 +10801,10 @@
       <c r="C77" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="9" t="s">
         <v>486</v>
       </c>
       <c r="F77" s="9" t="s">
@@ -10850,422 +10871,422 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>547</v>
       </c>
     </row>
@@ -11277,7 +11298,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -11285,13 +11306,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>498</v>
       </c>
     </row>
@@ -11313,7 +11334,7 @@
       <c r="B3" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>572</v>
       </c>
     </row>
@@ -11379,7 +11400,7 @@
       <c r="B9" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>588</v>
       </c>
     </row>
@@ -11390,7 +11411,7 @@
       <c r="B10" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>588</v>
       </c>
     </row>
@@ -11402,62 +11423,106 @@
         <v>592</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>595</v>
-      </c>
       <c r="C12" s="9" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>597</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B17" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>593</v>
+      <c r="C17" s="9" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>
